--- a/customer_service_forms/026_mario_form_2026_wedrive4u--customer_service_forms.xlsx
+++ b/customer_service_forms/026_mario_form_2026_wedrive4u--customer_service_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,8 +431,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +510,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>customer_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Customer Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -533,12 +533,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>visit_history</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Visit History</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_1</t>
+          <t>experience_rating</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>Experience Rating</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -579,12 +579,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -625,12 +625,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_2</t>
+          <t>contact_us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>second_page</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
